--- a/data/trans_orig/IP31KM06_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM06_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>25449</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19273</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>32398</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>47,38%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>35,88%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>60,31%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>21433</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>12477</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>29429</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>39,91%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>23,24%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>54,8%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>26336</t>
+          <t>20428</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20056</t>
+          <t>15252</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33724</t>
+          <t>26473</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>47769</t>
+          <t>45876</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36279</t>
+          <t>36514</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58465</t>
+          <t>55027</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>55,24%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>28266</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>21317</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>34442</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>52,62%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>39,69%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>64,12%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>32266</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>24270</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>41222</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>60,09%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>45,2%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>76,76%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>32009</t>
+          <t>25477</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24621</t>
+          <t>19432</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38289</t>
+          <t>30653</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>64274</t>
+          <t>53744</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53578</t>
+          <t>44593</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>75764</t>
+          <t>63106</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>63,35%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>184981</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>161377</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>208360</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>39,66%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>34,6%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>44,67%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>163305</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>138242</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>217919</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>36,14%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>30,6%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>48,23%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>197538</t>
+          <t>143574</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>174327</t>
+          <t>128291</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>228170</t>
+          <t>163452</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>360843</t>
+          <t>328555</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>325216</t>
+          <t>301736</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>423255</t>
+          <t>357432</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>40,11%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>281442</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>258063</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>305046</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>60,34%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>55,33%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>65,4%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>425</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>288527</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>233913</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>313590</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>63,86%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>51,77%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>69,4%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>307712</t>
+          <t>281092</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>277080</t>
+          <t>261214</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>330923</t>
+          <t>296375</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>596239</t>
+          <t>562535</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>533827</t>
+          <t>533658</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>631866</t>
+          <t>589354</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,14%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>625</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>54753</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>45394</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>66016</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>32,85%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>27,23%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>39,6%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>45392</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>35886</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>54643</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>31,05%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>24,55%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>37,38%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>60460</t>
+          <t>47201</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48674</t>
+          <t>37880</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72841</t>
+          <t>57516</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>105852</t>
+          <t>101954</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91575</t>
+          <t>88855</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>121657</t>
+          <t>116781</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,21%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>111933</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>100670</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>121292</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>67,15%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>60,4%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>72,77%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>100794</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>91543</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>110300</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>68,95%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>62,62%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>75,45%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>120679</t>
+          <t>99939</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>108298</t>
+          <t>89624</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>132465</t>
+          <t>109260</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>221472</t>
+          <t>211871</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>205667</t>
+          <t>197044</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>235749</t>
+          <t>224970</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>71,69%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,107 +1749,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>265182</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>241225</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>291196</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>38,61%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>35,12%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>42,4%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>290</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>230130</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>201649</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>287090</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>35,31%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>30,94%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>44,05%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>284334</t>
+          <t>211202</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>254866</t>
+          <t>192073</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>315021</t>
+          <t>234244</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>31,09%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>37,92%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>476384</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>446387</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>512491</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>36,52%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>34,22%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>42,3%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>514464</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>477698</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>571729</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>36,84%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>34,21%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>39,29%</t>
         </is>
       </c>
     </row>
@@ -1862,107 +1862,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>421642</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>395628</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>445599</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>61,39%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>57,6%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>64,88%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>624</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>421587</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>364627</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>450068</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>64,69%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>55,95%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>69,06%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>608</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>460399</t>
+          <t>406509</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>429712</t>
+          <t>383467</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>489867</t>
+          <t>425638</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>68,91%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1232</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>828151</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>792044</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>858148</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>63,48%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>60,71%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>65,78%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1232</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>881986</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>824721</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>918752</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>63,16%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>59,06%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>65,79%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
